--- a/outputs/solfacil/Solfacil_Securitizacoes_Comparativo.xlsx
+++ b/outputs/solfacil/Solfacil_Securitizacoes_Comparativo.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FIDC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CRI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Como ler" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIDC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como ler" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2565,37 +2565,30 @@
       <c r="B55" s="8">
         <f>SUM(B52:B54)</f>
         <v>83.7</v>
-        <v/>
       </c>
       <c r="C55" s="8">
         <f>SUM(C52:C54)</f>
         <v>94.0</v>
-        <v/>
       </c>
       <c r="D55" s="8">
         <f>SUM(D52:D54)</f>
         <v>17.5</v>
-        <v/>
       </c>
       <c r="E55" s="8">
         <f>SUM(E52:E54)</f>
         <v>67.5</v>
-        <v/>
       </c>
       <c r="F55" s="8">
         <f>SUM(F52:F54)</f>
         <v>141.1</v>
-        <v/>
       </c>
       <c r="G55" s="8">
         <f>SUM(G52:G54)</f>
         <v>211.0</v>
-        <v/>
       </c>
       <c r="H55" s="8">
         <f>SUM(H52:H54)</f>
         <v>619.7</v>
-        <v/>
       </c>
     </row>
     <row r="56">
@@ -2607,37 +2600,30 @@
       <c r="B56" s="9">
         <f>IF(B55=0,0,B52/B55)</f>
         <v>0.6356033453</v>
-        <v/>
       </c>
       <c r="C56" s="9">
         <f>IF(C55=0,0,C52/C55)</f>
         <v>0.7287234043</v>
-        <v/>
       </c>
       <c r="D56" s="9">
         <f>IF(D55=0,0,D52/D55)</f>
         <v>1.0</v>
-        <v/>
       </c>
       <c r="E56" s="9">
         <f>IF(E55=0,0,E52/E55)</f>
         <v>0.7911111111</v>
-        <v/>
       </c>
       <c r="F56" s="9">
         <f>IF(F55=0,0,F52/F55)</f>
         <v>0.6683203402</v>
-        <v/>
       </c>
       <c r="G56" s="9">
         <f>IF(G55=0,0,G52/G55)</f>
         <v>0.6639810427</v>
-        <v/>
       </c>
       <c r="H56" s="9">
         <f>IF(H55=0,0,H52/H55)</f>
         <v>0.7398741326</v>
-        <v/>
       </c>
     </row>
     <row r="57">
@@ -2649,37 +2635,30 @@
       <c r="B57" s="9">
         <f>IF(B55=0,0,B53/B55)</f>
         <v>0.3249701314</v>
-        <v/>
       </c>
       <c r="C57" s="9">
         <f>IF(C55=0,0,C53/C55)</f>
         <v>0.1489361702</v>
-        <v/>
       </c>
       <c r="D57" s="9">
         <f>IF(D55=0,0,D53/D55)</f>
         <v>0.0</v>
-        <v/>
       </c>
       <c r="E57" s="9">
         <f>IF(E55=0,0,E53/E55)</f>
         <v>0.1348148148</v>
-        <v/>
       </c>
       <c r="F57" s="9">
         <f>IF(F55=0,0,F53/F55)</f>
         <v>0.2097802977</v>
-        <v/>
       </c>
       <c r="G57" s="9">
         <f>IF(G55=0,0,G53/G55)</f>
         <v>0.1867298578</v>
-        <v/>
       </c>
       <c r="H57" s="9">
         <f>IF(H55=0,0,H53/H55)</f>
         <v>0.2078425044</v>
-        <v/>
       </c>
     </row>
     <row r="58">
@@ -2691,37 +2670,30 @@
       <c r="B58" s="9">
         <f>IF(B55=0,0,B54/B55)</f>
         <v>0.0394265233</v>
-        <v/>
       </c>
       <c r="C58" s="9">
         <f>IF(C55=0,0,C54/C55)</f>
         <v>0.1223404255</v>
-        <v/>
       </c>
       <c r="D58" s="9">
         <f>IF(D55=0,0,D54/D55)</f>
         <v>0.0</v>
-        <v/>
       </c>
       <c r="E58" s="9">
         <f>IF(E55=0,0,E54/E55)</f>
         <v>0.0740740741</v>
-        <v/>
       </c>
       <c r="F58" s="9">
         <f>IF(F55=0,0,F54/F55)</f>
         <v>0.1218993622</v>
-        <v/>
       </c>
       <c r="G58" s="9">
         <f>IF(G55=0,0,G54/G55)</f>
         <v>0.1492890995</v>
-        <v/>
       </c>
       <c r="H58" s="9">
         <f>IF(H55=0,0,H54/H55)</f>
         <v>0.0522833629</v>
-        <v/>
       </c>
     </row>
     <row r="59">
@@ -2733,37 +2705,30 @@
       <c r="B59" s="10">
         <f>IF(B55=0,0,(B53+B54)/B55)</f>
         <v>0.3643966547</v>
-        <v/>
       </c>
       <c r="C59" s="10">
         <f>IF(C55=0,0,(C53+C54)/C55)</f>
         <v>0.2712765957</v>
-        <v/>
       </c>
       <c r="D59" s="10">
         <f>IF(D55=0,0,(D53+D54)/D55)</f>
         <v>0.0</v>
-        <v/>
       </c>
       <c r="E59" s="10">
         <f>IF(E55=0,0,(E53+E54)/E55)</f>
         <v>0.2088888889</v>
-        <v/>
       </c>
       <c r="F59" s="10">
         <f>IF(F55=0,0,(F53+F54)/F55)</f>
         <v>0.3316796598</v>
-        <v/>
       </c>
       <c r="G59" s="10">
         <f>IF(G55=0,0,(G53+G54)/G55)</f>
         <v>0.3360189573</v>
-        <v/>
       </c>
       <c r="H59" s="10">
         <f>IF(H55=0,0,(H53+H54)/H55)</f>
         <v>0.2601258674</v>
-        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3268,12 +3233,10 @@
       <c r="B28" s="16">
         <f>SUM(B22:B27)</f>
         <v>470.599</v>
-        <v/>
       </c>
       <c r="C28" s="16">
         <f>SUM(C22:C27)</f>
         <v>627.647</v>
-        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
